--- a/Employee_Reports_wi52/Tharaka Thanujaya Dissanayaka Dissanayaka Mudiyanselage Q0573.xlsx
+++ b/Employee_Reports_wi52/Tharaka Thanujaya Dissanayaka Dissanayaka Mudiyanselage Q0573.xlsx
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -48,12 +48,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,15 +69,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -466,7 +457,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -548,123 +539,123 @@
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>18-Aug-2024</t>
+          <t>24-Aug-2026</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>18-Aug-2026</t>
+          <t>23-Aug-2028</t>
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-2</v>
+        <v>726</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>EXPIRED</t>
+          <t>VALID</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Essentials For Effective Communication (Other Trainings)</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>13-Nov-2025</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>13-Nov-2027</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n">
-        <v>450</v>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="H4" s="3" t="n">
+        <v>442</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Material request Procedure (Other Trainings)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>17-Nov-2024</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>17-Nov-2026</t>
         </is>
       </c>
-      <c r="H5" s="4" t="n">
-        <v>89</v>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="H5" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr"/>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr"/>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>YOU ARE LISTED AS ; TECHNICAL SUPPORT TEAM</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>&amp; THIS IS YOUR TRAINING DASHBOARD</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -733,52 +724,52 @@
       <c r="G2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ews Eq </t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>01-Nov-2023</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>95.00%</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Approved Score. date is valid</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n"/>
+      <c r="G3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr"/>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>TOTAL AVERAGE</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>95.00%</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="n"/>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
